--- a/XB6A/2. KL phân lớp cát đắp - XB6A.xlsx
+++ b/XB6A/2. KL phân lớp cát đắp - XB6A.xlsx
@@ -128,7 +128,7 @@
     <t xml:space="preserve">PHỤ LỤC KIỂM TRA CAO ĐỘ, KÍCH THƯỚC HÌNH HỌC ĐẮP CÁT</t>
   </si>
   <si>
-    <t xml:space="preserve">Kèm theo BBNT số: 04.NĐXB6A/CVXD ngày 16 tháng 08 năm 2026</t>
+    <t xml:space="preserve">Kèm theo BBNT số: 04.NĐXB6A/CVXD ngày 25 tháng 08 năm 2026</t>
   </si>
   <si>
     <t xml:space="preserve">Dự án: Xây dựng HTKT Khu tái định cư phục vụ di dân xã Hải Hà, thị xã Nghi Sơn, tỉnh Thanh Hóa.</t>
@@ -231,19 +231,19 @@
     <t xml:space="preserve">                 </t>
   </si>
   <si>
-    <t xml:space="preserve">Kèm theo BBNT số: 05.NĐXB6A/CVXD ngày 17 tháng 08 năm 2026</t>
+    <t xml:space="preserve">Kèm theo BBNT số: 05.NĐXB6A/CVXD ngày 26 tháng 08 năm 2026</t>
   </si>
   <si>
     <t xml:space="preserve">Đắp cát nền đường lớp 2 đoạn từ Km0+000,00 - Km0+126,46, độ chặt K&gt;=0,95</t>
   </si>
   <si>
-    <t xml:space="preserve">Kèm theo BBNT số: 06.NĐXB6A/CVXD ngày 24 tháng 08 năm 2026</t>
+    <t xml:space="preserve">Kèm theo BBNT số: 06.NĐXB6A/CVXD ngày 27 tháng 08 năm 2026</t>
   </si>
   <si>
     <t xml:space="preserve">Đắp cát nền đường lớp 3 đoạn từ Km0+000,00 - Km0+126,46, độ chặt K&gt;=0,95</t>
   </si>
   <si>
-    <t xml:space="preserve">Kèm theo BBNT số: 07.NĐXB6A/CVXD ngày 25 tháng 08 năm 2026</t>
+    <t xml:space="preserve">Kèm theo BBNT số: 07.NĐXB6A/CVXD ngày 28 tháng 08 năm 2026</t>
   </si>
   <si>
     <t xml:space="preserve">Đắp cát nền đường lớp 4 đoạn từ Km0+000,00 - Km0+126,46, độ chặt K&gt;=0,95</t>
@@ -1128,7 +1128,7 @@
             <v xml:space="preserve">Kiểm tra cao độ đường đen đoạn từ Km0+000,00 -:- Km0+126,46</v>
           </cell>
           <cell r="D3" t="str">
-            <v xml:space="preserve">ngày 14 tháng 08 năm 2026</v>
+            <v xml:space="preserve">ngày 20 tháng 08 năm 2026</v>
           </cell>
           <cell r="G3" t="str">
             <v xml:space="preserve">01.NĐXB6A/CVXD </v>
@@ -1142,7 +1142,7 @@
             <v xml:space="preserve">Đào đất xử lý nền đường đoạn từ Km0+000,00 - Km0+126,46</v>
           </cell>
           <cell r="D4" t="str">
-            <v xml:space="preserve">ngày 15 tháng 08 năm 2026</v>
+            <v xml:space="preserve">ngày 24 tháng 08 năm 2026</v>
           </cell>
           <cell r="G4" t="str">
             <v xml:space="preserve">02.NĐXB6A/CVXD </v>
@@ -1156,7 +1156,7 @@
             <v xml:space="preserve">Rải vải địa kỹ thuật đoạn từ Km0+000,00 - Km0+126,46</v>
           </cell>
           <cell r="D5" t="str">
-            <v xml:space="preserve">ngày 15 tháng 08 năm 2026</v>
+            <v xml:space="preserve">ngày 24 tháng 08 năm 2026</v>
           </cell>
           <cell r="G5" t="str">
             <v xml:space="preserve">03.NĐXB6A/CVXD </v>
@@ -1170,7 +1170,7 @@
             <v xml:space="preserve">Đắp cát nền đường lớp 1 đoạn từ Km0+000,00 - Km0+126,46, độ chặt K&gt;=0,95</v>
           </cell>
           <cell r="D6" t="str">
-            <v xml:space="preserve">ngày 16 tháng 08 năm 2026</v>
+            <v xml:space="preserve">ngày 25 tháng 08 năm 2026</v>
           </cell>
           <cell r="G6" t="str">
             <v xml:space="preserve">04.NĐXB6A/CVXD </v>
@@ -1184,7 +1184,7 @@
             <v xml:space="preserve">Đắp cát nền đường lớp 2 đoạn từ Km0+000,00 - Km0+126,46, độ chặt K&gt;=0,95</v>
           </cell>
           <cell r="D7" t="str">
-            <v xml:space="preserve">ngày 17 tháng 08 năm 2026</v>
+            <v xml:space="preserve">ngày 26 tháng 08 năm 2026</v>
           </cell>
           <cell r="G7" t="str">
             <v xml:space="preserve">05.NĐXB6A/CVXD </v>
@@ -1198,7 +1198,7 @@
             <v xml:space="preserve">Đắp cát nền đường lớp 3 đoạn từ Km0+000,00 - Km0+126,46, độ chặt K&gt;=0,95</v>
           </cell>
           <cell r="D8" t="str">
-            <v xml:space="preserve">ngày 24 tháng 08 năm 2026</v>
+            <v xml:space="preserve">ngày 27 tháng 08 năm 2026</v>
           </cell>
           <cell r="G8" t="str">
             <v xml:space="preserve">06.NĐXB6A/CVXD </v>
@@ -1212,7 +1212,7 @@
             <v xml:space="preserve">Đắp cát nền đường lớp 4 đoạn từ Km0+000,00 - Km0+126,46, độ chặt K&gt;=0,95</v>
           </cell>
           <cell r="D9" t="str">
-            <v xml:space="preserve">ngày 25 tháng 08 năm 2026</v>
+            <v xml:space="preserve">ngày 28 tháng 08 năm 2026</v>
           </cell>
           <cell r="G9" t="str">
             <v xml:space="preserve">07.NĐXB6A/CVXD </v>
@@ -1226,7 +1226,7 @@
             <v xml:space="preserve">Đắp đất nền đường lớp 1 đoạn từ Km0+000,00 - Km0+126,46, độ chặt K&gt;=0,95</v>
           </cell>
           <cell r="D10" t="str">
-            <v xml:space="preserve">ngày 26 tháng 08 năm 2026</v>
+            <v xml:space="preserve">ngày 29 tháng 08 năm 2026</v>
           </cell>
           <cell r="G10" t="str">
             <v xml:space="preserve">08.NĐXB6A/CVXD </v>
@@ -1240,7 +1240,7 @@
             <v xml:space="preserve">Đắp đất nền đường lớp 2 đoạn từ Km0+000,00 - Km0+126,46, độ chặt K&gt;=0,95</v>
           </cell>
           <cell r="D11" t="str">
-            <v xml:space="preserve">ngày 26 tháng 08 năm 2026</v>
+            <v xml:space="preserve">ngày 29 tháng 08 năm 2026</v>
           </cell>
           <cell r="G11" t="str">
             <v xml:space="preserve">09.NĐXB6A/CVXD </v>
@@ -1254,7 +1254,7 @@
             <v xml:space="preserve">Đắp đất nền đường lớp 3 đoạn từ Km0+000,00 - Km0+126,46, độ chặt K&gt;=0,95</v>
           </cell>
           <cell r="D12" t="str">
-            <v xml:space="preserve">ngày 27 tháng 08 năm 2026</v>
+            <v xml:space="preserve">ngày 30 tháng 08 năm 2026</v>
           </cell>
           <cell r="G12" t="str">
             <v xml:space="preserve">10.NĐXB6A/CVXD </v>
@@ -1268,7 +1268,7 @@
             <v xml:space="preserve">Đắp đất nền đường lớp 4 đoạn từ Km0+000,00 - Km0+126,46, độ chặt K&gt;=0,95</v>
           </cell>
           <cell r="D13" t="str">
-            <v xml:space="preserve">ngày 27 tháng 08 năm 2026</v>
+            <v xml:space="preserve">ngày 30 tháng 08 năm 2026</v>
           </cell>
           <cell r="G13" t="str">
             <v xml:space="preserve">11.NĐXB6A/CVXD </v>
@@ -1282,7 +1282,7 @@
             <v xml:space="preserve">Đắp đất nền đường lớp 5 đoạn từ Km0+000,00 - Km0+126,46, độ chặt K&gt;=0,95</v>
           </cell>
           <cell r="D14" t="str">
-            <v xml:space="preserve">ngày 28 tháng 08 năm 2026</v>
+            <v xml:space="preserve">ngày 03 tháng 09 năm 2026</v>
           </cell>
           <cell r="G14" t="str">
             <v xml:space="preserve">12.NĐXB6A/CVXD </v>
@@ -1296,7 +1296,7 @@
             <v xml:space="preserve">Đắp đất nền đường lớp 6 đoạn từ Km0+000,00 - Km0+126,46, độ chặt K&gt;=0,95</v>
           </cell>
           <cell r="D15" t="str">
-            <v xml:space="preserve">ngày 28 tháng 08 năm 2026</v>
+            <v xml:space="preserve">ngày 03 tháng 09 năm 2026</v>
           </cell>
           <cell r="G15" t="str">
             <v xml:space="preserve">13.NĐXB6A/CVXD </v>
@@ -1310,7 +1310,7 @@
             <v xml:space="preserve">Đắp đất nền đường lớp 7 đoạn từ Km0+000,00 - Km0+126,46, độ chặt K&gt;=0,95</v>
           </cell>
           <cell r="D16" t="str">
-            <v xml:space="preserve">ngày 29 tháng 08 năm 2026</v>
+            <v xml:space="preserve">ngày 04 tháng 09 năm 2026</v>
           </cell>
           <cell r="G16" t="str">
             <v xml:space="preserve">14.NĐXB6A/CVXD </v>
@@ -1324,7 +1324,7 @@
             <v xml:space="preserve">Đắp đất nền đường lớp 8 đoạn từ Km0+000,00 - Km0+126,46, độ chặt K&gt;=0,95</v>
           </cell>
           <cell r="D17" t="str">
-            <v xml:space="preserve">ngày 29 tháng 08 năm 2026</v>
+            <v xml:space="preserve">ngày 04 tháng 09 năm 2026</v>
           </cell>
           <cell r="G17" t="str">
             <v xml:space="preserve">15.NĐXB6A/CVXD </v>
@@ -1338,7 +1338,7 @@
             <v xml:space="preserve">Đắp đất nền đường lớp 9 đoạn từ Km0+000,00 - Km0+126,46, độ chặt K&gt;=0,95</v>
           </cell>
           <cell r="D18" t="str">
-            <v xml:space="preserve">ngày 30 tháng 08 năm 2026</v>
+            <v xml:space="preserve">ngày 05 tháng 09 năm 2026</v>
           </cell>
           <cell r="G18" t="str">
             <v xml:space="preserve">16.NĐXB6A/CVXD </v>
@@ -1352,7 +1352,7 @@
             <v xml:space="preserve">Đắp đất nền đường lớp 1, độ chặt K&gt;=0,98 đoạn từ Km0+000,00 - Km0+126,46</v>
           </cell>
           <cell r="D19" t="str">
-            <v xml:space="preserve">ngày 03 tháng 09 năm 2026</v>
+            <v xml:space="preserve">ngày 06 tháng 09 năm 2026</v>
           </cell>
           <cell r="G19" t="str">
             <v xml:space="preserve">17.NĐXB6A/CVXD </v>
@@ -1366,7 +1366,7 @@
             <v xml:space="preserve">Đắp đất lề đường lớp 1, độ chặt K&gt;=0,95 đoạn từ Km0+000,00 - Km0+126,46</v>
           </cell>
           <cell r="D20" t="str">
-            <v xml:space="preserve">ngày 03 tháng 09 năm 2026</v>
+            <v xml:space="preserve">ngày 06 tháng 09 năm 2026</v>
           </cell>
           <cell r="G20" t="str">
             <v xml:space="preserve">18.NĐXB6A/CVXD </v>
@@ -1380,7 +1380,7 @@
             <v xml:space="preserve">Đắp đất nền đường lớp 2, độ chặt K&gt;=0,98 đoạn từ Km0+000,00 - Km0+126,46</v>
           </cell>
           <cell r="D21" t="str">
-            <v xml:space="preserve">ngày 04 tháng 09 năm 2026</v>
+            <v xml:space="preserve">ngày 07 tháng 09 năm 2026</v>
           </cell>
           <cell r="G21" t="str">
             <v xml:space="preserve">19.NĐXB6A/CVXD </v>
@@ -1394,7 +1394,7 @@
             <v xml:space="preserve">Đắp đất lề đường lớp 2, độ chặt K&gt;=0,95 đoạn từ Km0+000,00 - Km0+126,46</v>
           </cell>
           <cell r="D22" t="str">
-            <v xml:space="preserve">ngày 04 tháng 09 năm 2026</v>
+            <v xml:space="preserve">ngày 07 tháng 09 năm 2026</v>
           </cell>
           <cell r="G22" t="str">
             <v xml:space="preserve">20.NĐXB6A/CVXD </v>
@@ -1408,7 +1408,7 @@
             <v xml:space="preserve">Đắp cấp phối đá dăm loại 2 đoạn từ Km0+000,00 - Km0+126,46</v>
           </cell>
           <cell r="D23" t="str">
-            <v xml:space="preserve">ngày 05 tháng 09 năm 2026</v>
+            <v xml:space="preserve">ngày 08 tháng 09 năm 2026</v>
           </cell>
           <cell r="G23" t="str">
             <v xml:space="preserve">21.NĐXB6A/CVXD </v>
@@ -1422,7 +1422,7 @@
             <v xml:space="preserve">Đắp đất lề đường lớp 3, độ chặt K&gt;=0,95 đoạn từ Km0+000,00 - Km0+126,46</v>
           </cell>
           <cell r="D24" t="str">
-            <v xml:space="preserve">ngày 05 tháng 09 năm 2026</v>
+            <v xml:space="preserve">ngày 08 tháng 09 năm 2026</v>
           </cell>
           <cell r="G24" t="str">
             <v xml:space="preserve">22.NĐXB6A/CVXD </v>
@@ -1436,7 +1436,7 @@
             <v xml:space="preserve">Đắp đất lề đường lớp 4, độ chặt K&gt;=0,95 đoạn từ Km0+000,00 - Km0+126,46</v>
           </cell>
           <cell r="D25" t="str">
-            <v xml:space="preserve">ngày 06 tháng 09 năm 2026</v>
+            <v xml:space="preserve">ngày 09 tháng 09 năm 2026</v>
           </cell>
           <cell r="G25" t="str">
             <v xml:space="preserve">23.NĐXB6A/CVXD </v>
@@ -1450,7 +1450,7 @@
             <v xml:space="preserve">Đắp cấp phối đá dăm loại 1 đoạn từ Km0+000,00 - Km0+126,46</v>
           </cell>
           <cell r="D26" t="str">
-            <v xml:space="preserve">ngày 06 tháng 09 năm 2026</v>
+            <v xml:space="preserve">ngày 09 tháng 09 năm 2026</v>
           </cell>
           <cell r="G26" t="str">
             <v xml:space="preserve">24.NĐXB6A/CVXD </v>
@@ -1464,7 +1464,7 @@
             <v xml:space="preserve">Vệ sinh, thổi bụi mặt đường </v>
           </cell>
           <cell r="D27" t="str">
-            <v xml:space="preserve">ngày 08 tháng 09 năm 2026</v>
+            <v xml:space="preserve">ngày 11 tháng 09 năm 2026</v>
           </cell>
           <cell r="G27" t="str">
             <v xml:space="preserve">25.NĐXB6A/CVXD </v>
@@ -1478,7 +1478,7 @@
             <v xml:space="preserve">Tưới lớp thấm bám mặt đường, nhựa MC70, lượng nhựa 1kg/m2</v>
           </cell>
           <cell r="D28" t="str">
-            <v xml:space="preserve">ngày 10 tháng 09 năm 2026</v>
+            <v xml:space="preserve">ngày 13 tháng 09 năm 2026</v>
           </cell>
           <cell r="G28" t="str">
             <v xml:space="preserve">26.NĐXB6A/CVXD </v>
@@ -1492,7 +1492,7 @@
             <v xml:space="preserve">Rải thảm mặt đường bê tông nhựa C16 - Chiều dày mặt đường đã lèn ép 6cm</v>
           </cell>
           <cell r="D29" t="str">
-            <v xml:space="preserve">ngày 12 tháng 09 năm 2026</v>
+            <v xml:space="preserve">ngày 19 tháng 09 năm 2026</v>
           </cell>
           <cell r="G29" t="str">
             <v xml:space="preserve">27.NĐXB6A/CVXD </v>
@@ -1506,7 +1506,7 @@
             <v xml:space="preserve">Bê tông nhựa C16 - Chiều dày mặt đường đã lèn ép 6cm</v>
           </cell>
           <cell r="D30" t="str">
-            <v xml:space="preserve">ngày 19 tháng 09 năm 2026</v>
+            <v xml:space="preserve">ngày 21 tháng 09 năm 2026</v>
           </cell>
           <cell r="G30" t="str">
             <v xml:space="preserve">28.NĐXB6A/CVXD </v>
@@ -2972,7 +2972,7 @@
     <row r="2" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="5" t="str">
         <f>"Kèm theo BBNT số: "&amp;VLOOKUP(AZ2,'[1]Tuyến XB6A'!$A$2:$G$60,7,0)&amp;VLOOKUP(AZ2,'[1]Tuyến XB6A'!$A$2:$G$60,4,0)</f>
-        <v xml:space="preserve">Kèm theo BBNT số: 04.NĐXB6A/CVXD ngày 16 tháng 08 năm 2026</v>
+        <v xml:space="preserve">Kèm theo BBNT số: 04.NĐXB6A/CVXD ngày 25 tháng 08 năm 2026</v>
       </c>
       <c r="B2" s="5"/>
       <c r="C2" s="5"/>
@@ -3294,11 +3294,11 @@
       </c>
       <c r="E24" s="17" t="n">
         <f aca="false">+D24+F24</f>
-        <v>-7.0788</v>
+        <v>-7.0667</v>
       </c>
       <c r="F24" s="17" t="n">
         <f aca="false">RANDBETWEEN(-105,115)/10000</f>
-        <v>-0.0088</v>
+        <v>0.0033</v>
       </c>
       <c r="G24" s="17" t="n">
         <f aca="false">+Chạy!G9</f>
@@ -3306,11 +3306,11 @@
       </c>
       <c r="H24" s="17" t="n">
         <f aca="false">G24+I24</f>
-        <v>-1.371</v>
+        <v>-1.355</v>
       </c>
       <c r="I24" s="17" t="n">
         <f aca="false">RANDBETWEEN(-30,90)/1000</f>
-        <v>-0.001</v>
+        <v>0.015</v>
       </c>
       <c r="J24" s="17" t="n">
         <f aca="false">+Chạy!K9</f>
@@ -3318,11 +3318,11 @@
       </c>
       <c r="K24" s="17" t="n">
         <f aca="false">J24+L24</f>
-        <v>-1.302</v>
+        <v>-1.341</v>
       </c>
       <c r="L24" s="17" t="n">
         <f aca="false">RANDBETWEEN(-30,90)/1000</f>
-        <v>0.068</v>
+        <v>0.029</v>
       </c>
       <c r="M24" s="17" t="n">
         <f aca="false">+Chạy!N9</f>
@@ -3330,11 +3330,11 @@
       </c>
       <c r="N24" s="17" t="n">
         <f aca="false">+M24+O24</f>
-        <v>7.1559</v>
+        <v>7.1411</v>
       </c>
       <c r="O24" s="17" t="n">
         <f aca="false">RANDBETWEEN(-105,115)/10000</f>
-        <v>0.0059</v>
+        <v>-0.0089</v>
       </c>
       <c r="P24" s="17" t="n">
         <f aca="false">+Chạy!O9</f>
@@ -3342,11 +3342,11 @@
       </c>
       <c r="Q24" s="17" t="n">
         <f aca="false">P24+R24</f>
-        <v>-1.386</v>
+        <v>-1.3</v>
       </c>
       <c r="R24" s="17" t="n">
         <f aca="false">RANDBETWEEN(-30,90)/1000</f>
-        <v>-0.016</v>
+        <v>0.07</v>
       </c>
       <c r="S24" s="18"/>
       <c r="T24" s="19" t="n">
@@ -3382,11 +3382,11 @@
       </c>
       <c r="H25" s="17" t="n">
         <f aca="false">G25+I25</f>
-        <v>-1.358</v>
+        <v>-1.336</v>
       </c>
       <c r="I25" s="17" t="n">
         <f aca="false">RANDBETWEEN(-30,90)/1000</f>
-        <v>0.052</v>
+        <v>0.074</v>
       </c>
       <c r="J25" s="17" t="n">
         <f aca="false">+Chạy!K13</f>
@@ -3394,11 +3394,11 @@
       </c>
       <c r="K25" s="17" t="n">
         <f aca="false">J25+L25</f>
-        <v>-1.435</v>
+        <v>-1.38</v>
       </c>
       <c r="L25" s="17" t="n">
         <f aca="false">RANDBETWEEN(-30,90)/1000</f>
-        <v>-0.025</v>
+        <v>0.03</v>
       </c>
       <c r="M25" s="17" t="n">
         <f aca="false">+Chạy!N13</f>
@@ -3406,11 +3406,11 @@
       </c>
       <c r="N25" s="17" t="n">
         <f aca="false">+M25+O25</f>
-        <v>7.1914</v>
+        <v>7.1818</v>
       </c>
       <c r="O25" s="17" t="n">
         <f aca="false">RANDBETWEEN(-105,115)/10000</f>
-        <v>0.0014</v>
+        <v>-0.0082</v>
       </c>
       <c r="P25" s="17" t="n">
         <f aca="false">+Chạy!O13</f>
@@ -3418,11 +3418,11 @@
       </c>
       <c r="Q25" s="17" t="n">
         <f aca="false">P25+R25</f>
-        <v>-1.404</v>
+        <v>-1.391</v>
       </c>
       <c r="R25" s="17" t="n">
         <f aca="false">RANDBETWEEN(-30,90)/1000</f>
-        <v>0.006</v>
+        <v>0.019</v>
       </c>
       <c r="S25" s="18"/>
       <c r="T25" s="19" t="n">
@@ -3446,11 +3446,11 @@
       </c>
       <c r="E26" s="17" t="n">
         <f aca="false">+D26+F26</f>
-        <v>-7.3849</v>
+        <v>-7.3807</v>
       </c>
       <c r="F26" s="17" t="n">
         <f aca="false">RANDBETWEEN(-105,115)/10000</f>
-        <v>-0.0049</v>
+        <v>-0.0007</v>
       </c>
       <c r="G26" s="17" t="n">
         <f aca="false">+Chạy!G17</f>
@@ -3458,11 +3458,11 @@
       </c>
       <c r="H26" s="17" t="n">
         <f aca="false">G26+I26</f>
-        <v>-1.479</v>
+        <v>-1.405</v>
       </c>
       <c r="I26" s="17" t="n">
         <f aca="false">RANDBETWEEN(-30,90)/1000</f>
-        <v>-0.019</v>
+        <v>0.055</v>
       </c>
       <c r="J26" s="17" t="n">
         <f aca="false">+Chạy!K17</f>
@@ -3470,11 +3470,11 @@
       </c>
       <c r="K26" s="17" t="n">
         <f aca="false">J26+L26</f>
-        <v>-1.39</v>
+        <v>-1.471</v>
       </c>
       <c r="L26" s="17" t="n">
         <f aca="false">RANDBETWEEN(-30,90)/1000</f>
-        <v>0.07</v>
+        <v>-0.011</v>
       </c>
       <c r="M26" s="17" t="n">
         <f aca="false">+Chạy!N17</f>
@@ -3482,11 +3482,11 @@
       </c>
       <c r="N26" s="17" t="n">
         <f aca="false">+M26+O26</f>
-        <v>7.3604</v>
+        <v>7.3518</v>
       </c>
       <c r="O26" s="17" t="n">
         <f aca="false">RANDBETWEEN(-105,115)/10000</f>
-        <v>0.0004</v>
+        <v>-0.0082</v>
       </c>
       <c r="P26" s="17" t="n">
         <f aca="false">+Chạy!O17</f>
@@ -3494,11 +3494,11 @@
       </c>
       <c r="Q26" s="17" t="n">
         <f aca="false">P26+R26</f>
-        <v>-1.443</v>
+        <v>-1.392</v>
       </c>
       <c r="R26" s="17" t="n">
         <f aca="false">RANDBETWEEN(-30,90)/1000</f>
-        <v>0.017</v>
+        <v>0.068</v>
       </c>
       <c r="S26" s="18"/>
       <c r="T26" s="19" t="n">
@@ -3553,11 +3553,11 @@
       </c>
       <c r="E28" s="17" t="n">
         <f aca="false">+D28+F28</f>
-        <v>-4.9131</v>
+        <v>-4.9164</v>
       </c>
       <c r="F28" s="17" t="n">
         <f aca="false">RANDBETWEEN(-105,115)/10000</f>
-        <v>0.0069</v>
+        <v>0.0036</v>
       </c>
       <c r="G28" s="17" t="n">
         <f aca="false">+Chạy!G25</f>
@@ -3565,11 +3565,11 @@
       </c>
       <c r="H28" s="17" t="n">
         <f aca="false">G28+I28</f>
-        <v>-1.45</v>
+        <v>-1.514</v>
       </c>
       <c r="I28" s="17" t="n">
         <f aca="false">RANDBETWEEN(-30,90)/1000</f>
-        <v>0.08</v>
+        <v>0.016</v>
       </c>
       <c r="J28" s="17" t="n">
         <f aca="false">+Chạy!K25</f>
@@ -3577,11 +3577,11 @@
       </c>
       <c r="K28" s="17" t="n">
         <f aca="false">J28+L28</f>
-        <v>-1.532</v>
+        <v>-1.521</v>
       </c>
       <c r="L28" s="17" t="n">
         <f aca="false">RANDBETWEEN(-30,90)/1000</f>
-        <v>-0.002</v>
+        <v>0.009</v>
       </c>
       <c r="M28" s="17" t="n">
         <f aca="false">+Chạy!N25</f>
@@ -3589,11 +3589,11 @@
       </c>
       <c r="N28" s="17" t="n">
         <f aca="false">+M28+O28</f>
-        <v>7.7719</v>
+        <v>7.7813</v>
       </c>
       <c r="O28" s="17" t="n">
         <f aca="false">RANDBETWEEN(-105,115)/10000</f>
-        <v>-0.0081</v>
+        <v>0.0013</v>
       </c>
       <c r="P28" s="17" t="n">
         <f aca="false">+Chạy!O25</f>
@@ -3601,11 +3601,11 @@
       </c>
       <c r="Q28" s="17" t="n">
         <f aca="false">P28+R28</f>
-        <v>-1.497</v>
+        <v>-1.524</v>
       </c>
       <c r="R28" s="17" t="n">
         <f aca="false">RANDBETWEEN(-30,90)/1000</f>
-        <v>0.033</v>
+        <v>0.006</v>
       </c>
       <c r="S28" s="18"/>
       <c r="T28" s="19" t="n">
@@ -3629,11 +3629,11 @@
       </c>
       <c r="E29" s="17" t="n">
         <f aca="false">+D29+F29</f>
-        <v>-7.7463</v>
+        <v>-7.7523</v>
       </c>
       <c r="F29" s="17" t="n">
         <f aca="false">RANDBETWEEN(-105,115)/10000</f>
-        <v>0.0037</v>
+        <v>-0.0023</v>
       </c>
       <c r="G29" s="17" t="n">
         <f aca="false">+Chạy!G29</f>
@@ -3641,11 +3641,11 @@
       </c>
       <c r="H29" s="17" t="n">
         <f aca="false">G29+I29</f>
-        <v>-1.496</v>
+        <v>-1.533</v>
       </c>
       <c r="I29" s="17" t="n">
         <f aca="false">RANDBETWEEN(-30,90)/1000</f>
-        <v>0.084</v>
+        <v>0.047</v>
       </c>
       <c r="J29" s="17" t="n">
         <f aca="false">+Chạy!K29</f>
@@ -3653,11 +3653,11 @@
       </c>
       <c r="K29" s="17" t="n">
         <f aca="false">J29+L29</f>
-        <v>-1.557</v>
+        <v>-1.55</v>
       </c>
       <c r="L29" s="17" t="n">
         <f aca="false">RANDBETWEEN(-30,90)/1000</f>
-        <v>0.023</v>
+        <v>0.03</v>
       </c>
       <c r="M29" s="17" t="n">
         <f aca="false">+Chạy!N29</f>
@@ -3665,11 +3665,11 @@
       </c>
       <c r="N29" s="17" t="n">
         <f aca="false">+M29+O29</f>
-        <v>7.4241</v>
+        <v>7.4237</v>
       </c>
       <c r="O29" s="17" t="n">
         <f aca="false">RANDBETWEEN(-105,115)/10000</f>
-        <v>0.0041</v>
+        <v>0.0037</v>
       </c>
       <c r="P29" s="17" t="n">
         <f aca="false">+Chạy!O29</f>
@@ -3677,11 +3677,11 @@
       </c>
       <c r="Q29" s="17" t="n">
         <f aca="false">P29+R29</f>
-        <v>-1.528</v>
+        <v>-1.554</v>
       </c>
       <c r="R29" s="17" t="n">
         <f aca="false">RANDBETWEEN(-30,90)/1000</f>
-        <v>0.052</v>
+        <v>0.026</v>
       </c>
       <c r="S29" s="18"/>
       <c r="T29" s="19" t="n">
@@ -3705,11 +3705,11 @@
       </c>
       <c r="E30" s="17" t="n">
         <f aca="false">+D30+F30</f>
-        <v>-7.7263</v>
+        <v>-7.7339</v>
       </c>
       <c r="F30" s="17" t="n">
         <f aca="false">RANDBETWEEN(-105,115)/10000</f>
-        <v>0.0037</v>
+        <v>-0.0039</v>
       </c>
       <c r="G30" s="17" t="n">
         <f aca="false">+Chạy!G33</f>
@@ -3717,11 +3717,11 @@
       </c>
       <c r="H30" s="17" t="n">
         <f aca="false">G30+I30</f>
-        <v>-1.559</v>
+        <v>-1.566</v>
       </c>
       <c r="I30" s="17" t="n">
         <f aca="false">RANDBETWEEN(-30,90)/1000</f>
-        <v>0.071</v>
+        <v>0.064</v>
       </c>
       <c r="J30" s="17" t="n">
         <f aca="false">+Chạy!K33</f>
@@ -3729,11 +3729,11 @@
       </c>
       <c r="K30" s="17" t="n">
         <f aca="false">J30+L30</f>
-        <v>-1.562</v>
+        <v>-1.627</v>
       </c>
       <c r="L30" s="17" t="n">
         <f aca="false">RANDBETWEEN(-30,90)/1000</f>
-        <v>0.068</v>
+        <v>0.003</v>
       </c>
       <c r="M30" s="17" t="n">
         <f aca="false">+Chạy!N33</f>
@@ -3741,11 +3741,11 @@
       </c>
       <c r="N30" s="17" t="n">
         <f aca="false">+M30+O30</f>
-        <v>7.252</v>
+        <v>7.2415</v>
       </c>
       <c r="O30" s="17" t="n">
         <f aca="false">RANDBETWEEN(-105,115)/10000</f>
-        <v>0.002</v>
+        <v>-0.0085</v>
       </c>
       <c r="P30" s="17" t="n">
         <f aca="false">+Chạy!O33</f>
@@ -3753,11 +3753,11 @@
       </c>
       <c r="Q30" s="17" t="n">
         <f aca="false">P30+R30</f>
-        <v>-1.62</v>
+        <v>-1.572</v>
       </c>
       <c r="R30" s="17" t="n">
         <f aca="false">RANDBETWEEN(-30,90)/1000</f>
-        <v>0.01</v>
+        <v>0.058</v>
       </c>
       <c r="S30" s="18"/>
       <c r="T30" s="19" t="n">
@@ -3986,7 +3986,7 @@
     <row r="2" s="26" customFormat="true" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="27" t="str">
         <f>"Kèm theo BBNT số: "&amp;VLOOKUP(AZ2,'[1]Tuyến XB6A'!$A$2:$G$60,7,0)&amp;VLOOKUP(AZ2,'[1]Tuyến XB6A'!$A$2:$G$60,4,0)</f>
-        <v xml:space="preserve">Kèm theo BBNT số: 04.NĐXB6A/CVXD ngày 16 tháng 08 năm 2026</v>
+        <v xml:space="preserve">Kèm theo BBNT số: 04.NĐXB6A/CVXD ngày 25 tháng 08 năm 2026</v>
       </c>
       <c r="B2" s="27"/>
       <c r="C2" s="27"/>
@@ -9146,7 +9146,7 @@
     <row r="2" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="5" t="str">
         <f>"Kèm theo BBNT số: "&amp;VLOOKUP(AZ2,'[1]Tuyến XB6A'!$A$2:$G$60,7,0)&amp;VLOOKUP(AZ2,'[1]Tuyến XB6A'!$A$2:$G$60,4,0)</f>
-        <v xml:space="preserve">Kèm theo BBNT số: 05.NĐXB6A/CVXD ngày 17 tháng 08 năm 2026</v>
+        <v xml:space="preserve">Kèm theo BBNT số: 05.NĐXB6A/CVXD ngày 26 tháng 08 năm 2026</v>
       </c>
       <c r="B2" s="5"/>
       <c r="C2" s="5"/>
@@ -9467,11 +9467,11 @@
       </c>
       <c r="E24" s="17" t="n">
         <f aca="false">+D24+F24</f>
-        <v>-7.3766</v>
+        <v>-7.3647</v>
       </c>
       <c r="F24" s="17" t="n">
         <f aca="false">RANDBETWEEN(-105,115)/10000</f>
-        <v>-0.0066</v>
+        <v>0.0053</v>
       </c>
       <c r="G24" s="17" t="n">
         <f aca="false">+Chạy!G8</f>
@@ -9479,11 +9479,11 @@
       </c>
       <c r="H24" s="17" t="n">
         <f aca="false">G24+I24</f>
-        <v>-1.022</v>
+        <v>-1.052</v>
       </c>
       <c r="I24" s="17" t="n">
         <f aca="false">RANDBETWEEN(-30,90)/1000</f>
-        <v>0.048</v>
+        <v>0.018</v>
       </c>
       <c r="J24" s="17" t="n">
         <f aca="false">+Chạy!K8</f>
@@ -9491,11 +9491,11 @@
       </c>
       <c r="K24" s="17" t="n">
         <f aca="false">J24+L24</f>
-        <v>-1.015</v>
+        <v>-0.995</v>
       </c>
       <c r="L24" s="17" t="n">
         <f aca="false">RANDBETWEEN(-30,90)/1000</f>
-        <v>0.055</v>
+        <v>0.075</v>
       </c>
       <c r="M24" s="17" t="n">
         <f aca="false">+Chạy!N8</f>
@@ -9503,11 +9503,11 @@
       </c>
       <c r="N24" s="17" t="n">
         <f aca="false">+M24+O24</f>
-        <v>7.4481</v>
+        <v>7.4492</v>
       </c>
       <c r="O24" s="17" t="n">
         <f aca="false">RANDBETWEEN(-105,115)/10000</f>
-        <v>-0.0019</v>
+        <v>-0.0008</v>
       </c>
       <c r="P24" s="17" t="n">
         <f aca="false">+Chạy!O8</f>
@@ -9515,11 +9515,11 @@
       </c>
       <c r="Q24" s="17" t="n">
         <f aca="false">P24+R24</f>
-        <v>-1.098</v>
+        <v>-1.092</v>
       </c>
       <c r="R24" s="17" t="n">
         <f aca="false">RANDBETWEEN(-30,90)/1000</f>
-        <v>-0.028</v>
+        <v>-0.022</v>
       </c>
       <c r="S24" s="18"/>
       <c r="T24" s="0" t="n">
@@ -9543,11 +9543,11 @@
       </c>
       <c r="E25" s="17" t="n">
         <f aca="false">+D25+F25</f>
-        <v>-7.4323</v>
+        <v>-7.4321</v>
       </c>
       <c r="F25" s="17" t="n">
         <f aca="false">RANDBETWEEN(-105,115)/10000</f>
-        <v>0.0077</v>
+        <v>0.0079</v>
       </c>
       <c r="G25" s="17" t="n">
         <f aca="false">+Chạy!G12</f>
@@ -9555,11 +9555,11 @@
       </c>
       <c r="H25" s="17" t="n">
         <f aca="false">G25+I25</f>
-        <v>-1.045</v>
+        <v>-1.053</v>
       </c>
       <c r="I25" s="17" t="n">
         <f aca="false">RANDBETWEEN(-30,90)/1000</f>
-        <v>0.065</v>
+        <v>0.057</v>
       </c>
       <c r="J25" s="17" t="n">
         <f aca="false">+Chạy!K12</f>
@@ -9567,11 +9567,11 @@
       </c>
       <c r="K25" s="17" t="n">
         <f aca="false">J25+L25</f>
-        <v>-1.132</v>
+        <v>-1.039</v>
       </c>
       <c r="L25" s="17" t="n">
         <f aca="false">RANDBETWEEN(-30,90)/1000</f>
-        <v>-0.022</v>
+        <v>0.071</v>
       </c>
       <c r="M25" s="17" t="n">
         <f aca="false">+Chạy!N12</f>
@@ -9579,11 +9579,11 @@
       </c>
       <c r="N25" s="17" t="n">
         <f aca="false">+M25+O25</f>
-        <v>7.501</v>
+        <v>7.4801</v>
       </c>
       <c r="O25" s="17" t="n">
         <f aca="false">RANDBETWEEN(-105,115)/10000</f>
-        <v>0.011</v>
+        <v>-0.0099</v>
       </c>
       <c r="P25" s="17" t="n">
         <f aca="false">+Chạy!O12</f>
@@ -9591,11 +9591,11 @@
       </c>
       <c r="Q25" s="17" t="n">
         <f aca="false">P25+R25</f>
-        <v>-1.094</v>
+        <v>-1.03</v>
       </c>
       <c r="R25" s="17" t="n">
         <f aca="false">RANDBETWEEN(-30,90)/1000</f>
-        <v>0.016</v>
+        <v>0.08</v>
       </c>
       <c r="S25" s="18"/>
       <c r="T25" s="0" t="n">
@@ -9619,11 +9619,11 @@
       </c>
       <c r="E26" s="17" t="n">
         <f aca="false">+D26+F26</f>
-        <v>-7.6767</v>
+        <v>-7.6775</v>
       </c>
       <c r="F26" s="17" t="n">
         <f aca="false">RANDBETWEEN(-105,115)/10000</f>
-        <v>0.0033</v>
+        <v>0.0025</v>
       </c>
       <c r="G26" s="17" t="n">
         <f aca="false">+Chạy!G16</f>
@@ -9631,11 +9631,11 @@
       </c>
       <c r="H26" s="17" t="n">
         <f aca="false">G26+I26</f>
-        <v>-1.141</v>
+        <v>-1.085</v>
       </c>
       <c r="I26" s="17" t="n">
         <f aca="false">RANDBETWEEN(-30,90)/1000</f>
-        <v>0.019</v>
+        <v>0.075</v>
       </c>
       <c r="J26" s="17" t="n">
         <f aca="false">+Chạy!K16</f>
@@ -9643,11 +9643,11 @@
       </c>
       <c r="K26" s="17" t="n">
         <f aca="false">J26+L26</f>
-        <v>-1.11</v>
+        <v>-1.089</v>
       </c>
       <c r="L26" s="17" t="n">
         <f aca="false">RANDBETWEEN(-30,90)/1000</f>
-        <v>0.05</v>
+        <v>0.071</v>
       </c>
       <c r="M26" s="17" t="n">
         <f aca="false">+Chạy!N16</f>
@@ -9655,11 +9655,11 @@
       </c>
       <c r="N26" s="17" t="n">
         <f aca="false">+M26+O26</f>
-        <v>7.6576</v>
+        <v>7.6527</v>
       </c>
       <c r="O26" s="17" t="n">
         <f aca="false">RANDBETWEEN(-105,115)/10000</f>
-        <v>-0.0024</v>
+        <v>-0.0073</v>
       </c>
       <c r="P26" s="17" t="n">
         <f aca="false">+Chạy!O16</f>
@@ -9667,11 +9667,11 @@
       </c>
       <c r="Q26" s="17" t="n">
         <f aca="false">P26+R26</f>
-        <v>-1.07</v>
+        <v>-1.092</v>
       </c>
       <c r="R26" s="17" t="n">
         <f aca="false">RANDBETWEEN(-30,90)/1000</f>
-        <v>0.09</v>
+        <v>0.068</v>
       </c>
       <c r="S26" s="18"/>
       <c r="T26" s="0" t="n">
@@ -9726,11 +9726,11 @@
       </c>
       <c r="E28" s="17" t="n">
         <f aca="false">+D28+F28</f>
-        <v>-5.2232</v>
+        <v>-5.2131</v>
       </c>
       <c r="F28" s="17" t="n">
         <f aca="false">RANDBETWEEN(-105,115)/10000</f>
-        <v>-0.0032</v>
+        <v>0.0069</v>
       </c>
       <c r="G28" s="17" t="n">
         <f aca="false">+Chạy!G24</f>
@@ -9738,11 +9738,11 @@
       </c>
       <c r="H28" s="17" t="n">
         <f aca="false">G28+I28</f>
-        <v>-1.185</v>
+        <v>-1.178</v>
       </c>
       <c r="I28" s="17" t="n">
         <f aca="false">RANDBETWEEN(-30,90)/1000</f>
-        <v>0.045</v>
+        <v>0.052</v>
       </c>
       <c r="J28" s="17" t="n">
         <f aca="false">+Chạy!K24</f>
@@ -9750,11 +9750,11 @@
       </c>
       <c r="K28" s="17" t="n">
         <f aca="false">J28+L28</f>
-        <v>-1.157</v>
+        <v>-1.211</v>
       </c>
       <c r="L28" s="17" t="n">
         <f aca="false">RANDBETWEEN(-30,90)/1000</f>
-        <v>0.073</v>
+        <v>0.019</v>
       </c>
       <c r="M28" s="17" t="n">
         <f aca="false">+Chạy!N24</f>
@@ -9762,11 +9762,11 @@
       </c>
       <c r="N28" s="17" t="n">
         <f aca="false">+M28+O28</f>
-        <v>8.0744</v>
+        <v>8.0849</v>
       </c>
       <c r="O28" s="17" t="n">
         <f aca="false">RANDBETWEEN(-105,115)/10000</f>
-        <v>-0.0056</v>
+        <v>0.0049</v>
       </c>
       <c r="P28" s="17" t="n">
         <f aca="false">+Chạy!O24</f>
@@ -9774,11 +9774,11 @@
       </c>
       <c r="Q28" s="17" t="n">
         <f aca="false">P28+R28</f>
-        <v>-1.154</v>
+        <v>-1.193</v>
       </c>
       <c r="R28" s="17" t="n">
         <f aca="false">RANDBETWEEN(-30,90)/1000</f>
-        <v>0.076</v>
+        <v>0.037</v>
       </c>
       <c r="S28" s="18"/>
       <c r="T28" s="0" t="n">
@@ -9802,11 +9802,11 @@
       </c>
       <c r="E29" s="17" t="n">
         <f aca="false">+D29+F29</f>
-        <v>-8.0585</v>
+        <v>-8.0518</v>
       </c>
       <c r="F29" s="17" t="n">
         <f aca="false">RANDBETWEEN(-105,115)/10000</f>
-        <v>-0.0085</v>
+        <v>-0.0018</v>
       </c>
       <c r="G29" s="17" t="n">
         <f aca="false">+Chạy!G28</f>
@@ -9814,11 +9814,11 @@
       </c>
       <c r="H29" s="17" t="n">
         <f aca="false">G29+I29</f>
-        <v>-1.232</v>
+        <v>-1.208</v>
       </c>
       <c r="I29" s="17" t="n">
         <f aca="false">RANDBETWEEN(-30,90)/1000</f>
-        <v>0.048</v>
+        <v>0.072</v>
       </c>
       <c r="J29" s="17" t="n">
         <f aca="false">+Chạy!K28</f>
@@ -9826,11 +9826,11 @@
       </c>
       <c r="K29" s="17" t="n">
         <f aca="false">J29+L29</f>
-        <v>-1.242</v>
+        <v>-1.231</v>
       </c>
       <c r="L29" s="17" t="n">
         <f aca="false">RANDBETWEEN(-30,90)/1000</f>
-        <v>0.038</v>
+        <v>0.049</v>
       </c>
       <c r="M29" s="17" t="n">
         <f aca="false">+Chạy!N28</f>
@@ -9838,11 +9838,11 @@
       </c>
       <c r="N29" s="17" t="n">
         <f aca="false">+M29+O29</f>
-        <v>7.7276</v>
+        <v>7.7253</v>
       </c>
       <c r="O29" s="17" t="n">
         <f aca="false">RANDBETWEEN(-105,115)/10000</f>
-        <v>0.0076</v>
+        <v>0.0053</v>
       </c>
       <c r="P29" s="17" t="n">
         <f aca="false">+Chạy!O28</f>
@@ -9850,11 +9850,11 @@
       </c>
       <c r="Q29" s="17" t="n">
         <f aca="false">P29+R29</f>
-        <v>-1.25</v>
+        <v>-1.297</v>
       </c>
       <c r="R29" s="17" t="n">
         <f aca="false">RANDBETWEEN(-30,90)/1000</f>
-        <v>0.03</v>
+        <v>-0.017</v>
       </c>
       <c r="S29" s="18"/>
       <c r="T29" s="0" t="n">
@@ -9878,11 +9878,11 @@
       </c>
       <c r="E30" s="17" t="n">
         <f aca="false">+D30+F30</f>
-        <v>-8.0233</v>
+        <v>-8.0247</v>
       </c>
       <c r="F30" s="17" t="n">
         <f aca="false">RANDBETWEEN(-105,115)/10000</f>
-        <v>0.0067</v>
+        <v>0.0053</v>
       </c>
       <c r="G30" s="17" t="n">
         <f aca="false">+Chạy!G32</f>
@@ -9890,11 +9890,11 @@
       </c>
       <c r="H30" s="17" t="n">
         <f aca="false">G30+I30</f>
-        <v>-1.281</v>
+        <v>-1.25</v>
       </c>
       <c r="I30" s="17" t="n">
         <f aca="false">RANDBETWEEN(-30,90)/1000</f>
-        <v>0.049</v>
+        <v>0.08</v>
       </c>
       <c r="J30" s="17" t="n">
         <f aca="false">+Chạy!K32</f>
@@ -9902,11 +9902,11 @@
       </c>
       <c r="K30" s="17" t="n">
         <f aca="false">J30+L30</f>
-        <v>-1.342</v>
+        <v>-1.294</v>
       </c>
       <c r="L30" s="17" t="n">
         <f aca="false">RANDBETWEEN(-30,90)/1000</f>
-        <v>-0.012</v>
+        <v>0.036</v>
       </c>
       <c r="M30" s="17" t="n">
         <f aca="false">+Chạy!N32</f>
@@ -9914,11 +9914,11 @@
       </c>
       <c r="N30" s="17" t="n">
         <f aca="false">+M30+O30</f>
-        <v>7.5611</v>
+        <v>7.554</v>
       </c>
       <c r="O30" s="17" t="n">
         <f aca="false">RANDBETWEEN(-105,115)/10000</f>
-        <v>0.0111</v>
+        <v>0.004</v>
       </c>
       <c r="P30" s="17" t="n">
         <f aca="false">+Chạy!O32</f>
@@ -9926,11 +9926,11 @@
       </c>
       <c r="Q30" s="17" t="n">
         <f aca="false">P30+R30</f>
-        <v>-1.327</v>
+        <v>-1.316</v>
       </c>
       <c r="R30" s="17" t="n">
         <f aca="false">RANDBETWEEN(-30,90)/1000</f>
-        <v>0.003</v>
+        <v>0.014</v>
       </c>
       <c r="S30" s="18"/>
       <c r="T30" s="0" t="n">
@@ -10156,7 +10156,7 @@
     <row r="2" s="26" customFormat="true" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="27" t="str">
         <f>"Kèm theo BBNT số: "&amp;VLOOKUP(AZ2,'[1]Tuyến XB6A'!$A$2:$G$60,7,0)&amp;VLOOKUP(AZ2,'[1]Tuyến XB6A'!$A$2:$G$60,4,0)</f>
-        <v xml:space="preserve">Kèm theo BBNT số: 05.NĐXB6A/CVXD ngày 17 tháng 08 năm 2026</v>
+        <v xml:space="preserve">Kèm theo BBNT số: 05.NĐXB6A/CVXD ngày 26 tháng 08 năm 2026</v>
       </c>
       <c r="B2" s="27"/>
       <c r="C2" s="27"/>
@@ -15308,7 +15308,7 @@
     <row r="2" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="5" t="str">
         <f>"Kèm theo BBNT số: "&amp;VLOOKUP(AZ2,'[1]Tuyến XB6A'!$A$2:$G$60,7,0)&amp;VLOOKUP(AZ2,'[1]Tuyến XB6A'!$A$2:$G$60,4,0)</f>
-        <v xml:space="preserve">Kèm theo BBNT số: 06.NĐXB6A/CVXD ngày 24 tháng 08 năm 2026</v>
+        <v xml:space="preserve">Kèm theo BBNT số: 06.NĐXB6A/CVXD ngày 27 tháng 08 năm 2026</v>
       </c>
       <c r="B2" s="5"/>
       <c r="C2" s="5"/>
@@ -15628,11 +15628,11 @@
       </c>
       <c r="E23" s="17" t="n">
         <f aca="false">+D23+F23</f>
-        <v>-7.6742</v>
+        <v>-7.6715</v>
       </c>
       <c r="F23" s="17" t="n">
         <f aca="false">RANDBETWEEN(-105,115)/10000</f>
-        <v>-0.0042</v>
+        <v>-0.0015</v>
       </c>
       <c r="G23" s="17" t="n">
         <f aca="false">+Chạy!G7</f>
@@ -15640,11 +15640,11 @@
       </c>
       <c r="H23" s="17" t="n">
         <f aca="false">G23+I23</f>
-        <v>-0.686</v>
+        <v>-0.772</v>
       </c>
       <c r="I23" s="17" t="n">
         <f aca="false">RANDBETWEEN(-30,90)/1000</f>
-        <v>0.084</v>
+        <v>-0.002</v>
       </c>
       <c r="J23" s="17" t="n">
         <f aca="false">+Chạy!K7</f>
@@ -15652,11 +15652,11 @@
       </c>
       <c r="K23" s="17" t="n">
         <f aca="false">J23+L23</f>
-        <v>-0.711</v>
+        <v>-0.688</v>
       </c>
       <c r="L23" s="17" t="n">
         <f aca="false">RANDBETWEEN(-30,90)/1000</f>
-        <v>0.059</v>
+        <v>0.082</v>
       </c>
       <c r="M23" s="17" t="n">
         <f aca="false">+Chạy!N7</f>
@@ -15664,11 +15664,11 @@
       </c>
       <c r="N23" s="17" t="n">
         <f aca="false">+M23+O23</f>
-        <v>7.7465</v>
+        <v>7.7401</v>
       </c>
       <c r="O23" s="17" t="n">
         <f aca="false">RANDBETWEEN(-105,115)/10000</f>
-        <v>-0.0035</v>
+        <v>-0.0099</v>
       </c>
       <c r="P23" s="17" t="n">
         <f aca="false">+Chạy!O7</f>
@@ -15676,11 +15676,11 @@
       </c>
       <c r="Q23" s="17" t="n">
         <f aca="false">P23+R23</f>
-        <v>-0.707</v>
+        <v>-0.776</v>
       </c>
       <c r="R23" s="17" t="n">
         <f aca="false">RANDBETWEEN(-30,90)/1000</f>
-        <v>0.063</v>
+        <v>-0.006</v>
       </c>
       <c r="S23" s="18"/>
       <c r="T23" s="0" t="n">
@@ -15704,11 +15704,11 @@
       </c>
       <c r="E24" s="17" t="n">
         <f aca="false">+D24+F24</f>
-        <v>-7.7353</v>
+        <v>-7.7306</v>
       </c>
       <c r="F24" s="17" t="n">
         <f aca="false">RANDBETWEEN(-105,115)/10000</f>
-        <v>0.0047</v>
+        <v>0.0094</v>
       </c>
       <c r="G24" s="17" t="n">
         <f aca="false">+Chạy!G11</f>
@@ -15716,11 +15716,11 @@
       </c>
       <c r="H24" s="17" t="n">
         <f aca="false">G24+I24</f>
-        <v>-0.769</v>
+        <v>-0.74</v>
       </c>
       <c r="I24" s="17" t="n">
         <f aca="false">RANDBETWEEN(-30,90)/1000</f>
-        <v>0.041</v>
+        <v>0.07</v>
       </c>
       <c r="J24" s="17" t="n">
         <f aca="false">+Chạy!K11</f>
@@ -15728,11 +15728,11 @@
       </c>
       <c r="K24" s="17" t="n">
         <f aca="false">J24+L24</f>
-        <v>-0.817</v>
+        <v>-0.826</v>
       </c>
       <c r="L24" s="17" t="n">
         <f aca="false">RANDBETWEEN(-30,90)/1000</f>
-        <v>-0.007</v>
+        <v>-0.016</v>
       </c>
       <c r="M24" s="17" t="n">
         <f aca="false">+Chạy!N11</f>
@@ -15740,11 +15740,11 @@
       </c>
       <c r="N24" s="17" t="n">
         <f aca="false">+M24+O24</f>
-        <v>7.7963</v>
+        <v>7.7939</v>
       </c>
       <c r="O24" s="17" t="n">
         <f aca="false">RANDBETWEEN(-105,115)/10000</f>
-        <v>0.0063</v>
+        <v>0.0039</v>
       </c>
       <c r="P24" s="17" t="n">
         <f aca="false">+Chạy!O11</f>
@@ -15752,11 +15752,11 @@
       </c>
       <c r="Q24" s="17" t="n">
         <f aca="false">P24+R24</f>
-        <v>-0.756</v>
+        <v>-0.787</v>
       </c>
       <c r="R24" s="17" t="n">
         <f aca="false">RANDBETWEEN(-30,90)/1000</f>
-        <v>0.054</v>
+        <v>0.023</v>
       </c>
       <c r="S24" s="18"/>
       <c r="T24" s="0" t="n">
@@ -15780,11 +15780,11 @@
       </c>
       <c r="E25" s="17" t="n">
         <f aca="false">+D25+F25</f>
-        <v>-7.9771</v>
+        <v>-7.9897</v>
       </c>
       <c r="F25" s="17" t="n">
         <f aca="false">RANDBETWEEN(-105,115)/10000</f>
-        <v>0.0029</v>
+        <v>-0.0097</v>
       </c>
       <c r="G25" s="17" t="n">
         <f aca="false">+Chạy!G15</f>
@@ -15792,11 +15792,11 @@
       </c>
       <c r="H25" s="17" t="n">
         <f aca="false">G25+I25</f>
-        <v>-0.836</v>
+        <v>-0.773</v>
       </c>
       <c r="I25" s="17" t="n">
         <f aca="false">RANDBETWEEN(-30,90)/1000</f>
-        <v>0.024</v>
+        <v>0.087</v>
       </c>
       <c r="J25" s="17" t="n">
         <f aca="false">+Chạy!K15</f>
@@ -15804,11 +15804,11 @@
       </c>
       <c r="K25" s="17" t="n">
         <f aca="false">J25+L25</f>
-        <v>-0.79</v>
+        <v>-0.873</v>
       </c>
       <c r="L25" s="17" t="n">
         <f aca="false">RANDBETWEEN(-30,90)/1000</f>
-        <v>0.07</v>
+        <v>-0.013</v>
       </c>
       <c r="M25" s="17" t="n">
         <f aca="false">+Chạy!N15</f>
@@ -15816,11 +15816,11 @@
       </c>
       <c r="N25" s="17" t="n">
         <f aca="false">+M25+O25</f>
-        <v>7.9547</v>
+        <v>7.9662</v>
       </c>
       <c r="O25" s="17" t="n">
         <f aca="false">RANDBETWEEN(-105,115)/10000</f>
-        <v>-0.0053</v>
+        <v>0.0062</v>
       </c>
       <c r="P25" s="17" t="n">
         <f aca="false">+Chạy!O15</f>
@@ -15828,11 +15828,11 @@
       </c>
       <c r="Q25" s="17" t="n">
         <f aca="false">P25+R25</f>
-        <v>-0.773</v>
+        <v>-0.86</v>
       </c>
       <c r="R25" s="17" t="n">
         <f aca="false">RANDBETWEEN(-30,90)/1000</f>
-        <v>0.087</v>
+        <v>0</v>
       </c>
       <c r="S25" s="18"/>
       <c r="T25" s="0" t="n">
@@ -15887,11 +15887,11 @@
       </c>
       <c r="E27" s="17" t="n">
         <f aca="false">+D27+F27</f>
-        <v>-5.5104</v>
+        <v>-5.5262</v>
       </c>
       <c r="F27" s="17" t="n">
         <f aca="false">RANDBETWEEN(-105,115)/10000</f>
-        <v>0.0096</v>
+        <v>-0.0062</v>
       </c>
       <c r="G27" s="17" t="n">
         <f aca="false">+Chạy!G23</f>
@@ -15899,11 +15899,11 @@
       </c>
       <c r="H27" s="17" t="n">
         <f aca="false">G27+I27</f>
-        <v>-0.948</v>
+        <v>-0.868</v>
       </c>
       <c r="I27" s="17" t="n">
         <f aca="false">RANDBETWEEN(-30,90)/1000</f>
-        <v>-0.018</v>
+        <v>0.062</v>
       </c>
       <c r="J27" s="17" t="n">
         <f aca="false">+Chạy!K23</f>
@@ -15911,11 +15911,11 @@
       </c>
       <c r="K27" s="17" t="n">
         <f aca="false">J27+L27</f>
-        <v>-0.896</v>
+        <v>-0.868</v>
       </c>
       <c r="L27" s="17" t="n">
         <f aca="false">RANDBETWEEN(-30,90)/1000</f>
-        <v>0.034</v>
+        <v>0.062</v>
       </c>
       <c r="M27" s="17" t="n">
         <f aca="false">+Chạy!N23</f>
@@ -15923,11 +15923,11 @@
       </c>
       <c r="N27" s="17" t="n">
         <f aca="false">+M27+O27</f>
-        <v>8.3911</v>
+        <v>8.3745</v>
       </c>
       <c r="O27" s="17" t="n">
         <f aca="false">RANDBETWEEN(-105,115)/10000</f>
-        <v>0.0111</v>
+        <v>-0.0055</v>
       </c>
       <c r="P27" s="17" t="n">
         <f aca="false">+Chạy!O23</f>
@@ -15935,11 +15935,11 @@
       </c>
       <c r="Q27" s="17" t="n">
         <f aca="false">P27+R27</f>
-        <v>-0.844</v>
+        <v>-0.931</v>
       </c>
       <c r="R27" s="17" t="n">
         <f aca="false">RANDBETWEEN(-30,90)/1000</f>
-        <v>0.086</v>
+        <v>-0.001</v>
       </c>
       <c r="S27" s="18"/>
       <c r="T27" s="0" t="n">
@@ -15963,11 +15963,11 @@
       </c>
       <c r="E28" s="17" t="n">
         <f aca="false">+D28+F28</f>
-        <v>-8.3432</v>
+        <v>-8.3537</v>
       </c>
       <c r="F28" s="17" t="n">
         <f aca="false">RANDBETWEEN(-105,115)/10000</f>
-        <v>0.0068</v>
+        <v>-0.0037</v>
       </c>
       <c r="G28" s="17" t="n">
         <f aca="false">+Chạy!G27</f>
@@ -15975,11 +15975,11 @@
       </c>
       <c r="H28" s="17" t="n">
         <f aca="false">G28+I28</f>
-        <v>-0.97</v>
+        <v>-0.967</v>
       </c>
       <c r="I28" s="17" t="n">
         <f aca="false">RANDBETWEEN(-30,90)/1000</f>
-        <v>0.01</v>
+        <v>0.013</v>
       </c>
       <c r="J28" s="17" t="n">
         <f aca="false">+Chạy!K27</f>
@@ -15987,11 +15987,11 @@
       </c>
       <c r="K28" s="17" t="n">
         <f aca="false">J28+L28</f>
-        <v>-0.972</v>
+        <v>-0.937</v>
       </c>
       <c r="L28" s="17" t="n">
         <f aca="false">RANDBETWEEN(-30,90)/1000</f>
-        <v>0.008</v>
+        <v>0.043</v>
       </c>
       <c r="M28" s="17" t="n">
         <f aca="false">+Chạy!N27</f>
@@ -15999,11 +15999,11 @@
       </c>
       <c r="N28" s="17" t="n">
         <f aca="false">+M28+O28</f>
-        <v>8.0192</v>
+        <v>8.0164</v>
       </c>
       <c r="O28" s="17" t="n">
         <f aca="false">RANDBETWEEN(-105,115)/10000</f>
-        <v>-0.0008</v>
+        <v>-0.0036</v>
       </c>
       <c r="P28" s="17" t="n">
         <f aca="false">+Chạy!O27</f>
@@ -16011,11 +16011,11 @@
       </c>
       <c r="Q28" s="17" t="n">
         <f aca="false">P28+R28</f>
-        <v>-0.892</v>
+        <v>-0.911</v>
       </c>
       <c r="R28" s="17" t="n">
         <f aca="false">RANDBETWEEN(-30,90)/1000</f>
-        <v>0.088</v>
+        <v>0.069</v>
       </c>
       <c r="S28" s="18"/>
       <c r="T28" s="0" t="n">
@@ -16039,11 +16039,11 @@
       </c>
       <c r="E29" s="17" t="n">
         <f aca="false">+D29+F29</f>
-        <v>-8.3405</v>
+        <v>-8.3198</v>
       </c>
       <c r="F29" s="17" t="n">
         <f aca="false">RANDBETWEEN(-105,115)/10000</f>
-        <v>-0.0105</v>
+        <v>0.0102</v>
       </c>
       <c r="G29" s="17" t="n">
         <f aca="false">+Chạy!G31</f>
@@ -16051,11 +16051,11 @@
       </c>
       <c r="H29" s="17" t="n">
         <f aca="false">G29+I29</f>
-        <v>-0.973</v>
+        <v>-0.993</v>
       </c>
       <c r="I29" s="17" t="n">
         <f aca="false">RANDBETWEEN(-30,90)/1000</f>
-        <v>0.057</v>
+        <v>0.037</v>
       </c>
       <c r="J29" s="17" t="n">
         <f aca="false">+Chạy!K31</f>
@@ -16063,11 +16063,11 @@
       </c>
       <c r="K29" s="17" t="n">
         <f aca="false">J29+L29</f>
-        <v>-0.995</v>
+        <v>-0.954</v>
       </c>
       <c r="L29" s="17" t="n">
         <f aca="false">RANDBETWEEN(-30,90)/1000</f>
-        <v>0.035</v>
+        <v>0.076</v>
       </c>
       <c r="M29" s="17" t="n">
         <f aca="false">+Chạy!N31</f>
@@ -16075,11 +16075,11 @@
       </c>
       <c r="N29" s="17" t="n">
         <f aca="false">+M29+O29</f>
-        <v>7.8413</v>
+        <v>7.8434</v>
       </c>
       <c r="O29" s="17" t="n">
         <f aca="false">RANDBETWEEN(-105,115)/10000</f>
-        <v>-0.0087</v>
+        <v>-0.0066</v>
       </c>
       <c r="P29" s="17" t="n">
         <f aca="false">+Chạy!O31</f>
@@ -16087,11 +16087,11 @@
       </c>
       <c r="Q29" s="17" t="n">
         <f aca="false">P29+R29</f>
-        <v>-0.987</v>
+        <v>-0.956</v>
       </c>
       <c r="R29" s="17" t="n">
         <f aca="false">RANDBETWEEN(-30,90)/1000</f>
-        <v>0.043</v>
+        <v>0.074</v>
       </c>
       <c r="S29" s="18"/>
       <c r="T29" s="0" t="n">
@@ -16317,7 +16317,7 @@
     <row r="2" s="26" customFormat="true" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="27" t="str">
         <f>"Kèm theo BBNT số: "&amp;VLOOKUP(AZ2,'[1]Tuyến XB6A'!$A$2:$G$60,7,0)&amp;VLOOKUP(AZ2,'[1]Tuyến XB6A'!$A$2:$G$60,4,0)</f>
-        <v xml:space="preserve">Kèm theo BBNT số: 06.NĐXB6A/CVXD ngày 24 tháng 08 năm 2026</v>
+        <v xml:space="preserve">Kèm theo BBNT số: 06.NĐXB6A/CVXD ngày 27 tháng 08 năm 2026</v>
       </c>
       <c r="B2" s="27"/>
       <c r="C2" s="27"/>
@@ -21470,7 +21470,7 @@
     <row r="2" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="5" t="str">
         <f>"Kèm theo BBNT số: "&amp;VLOOKUP(AZ2,'[1]Tuyến XB6A'!$A$2:$G$60,7,0)&amp;VLOOKUP(AZ2,'[1]Tuyến XB6A'!$A$2:$G$60,4,0)</f>
-        <v xml:space="preserve">Kèm theo BBNT số: 07.NĐXB6A/CVXD ngày 25 tháng 08 năm 2026</v>
+        <v xml:space="preserve">Kèm theo BBNT số: 07.NĐXB6A/CVXD ngày 28 tháng 08 năm 2026</v>
       </c>
       <c r="B2" s="5"/>
       <c r="C2" s="5"/>
@@ -21792,11 +21792,11 @@
       </c>
       <c r="E24" s="17" t="n">
         <f aca="false">+D24+F24</f>
-        <v>-7.9796</v>
+        <v>-7.9799</v>
       </c>
       <c r="F24" s="17" t="n">
         <f aca="false">RANDBETWEEN(-105,115)/10000</f>
-        <v>-0.0096</v>
+        <v>-0.0099</v>
       </c>
       <c r="G24" s="17" t="n">
         <f aca="false">+Chạy!G6</f>
@@ -21804,11 +21804,11 @@
       </c>
       <c r="H24" s="17" t="n">
         <f aca="false">G24+I24</f>
-        <v>-0.453</v>
+        <v>-0.405</v>
       </c>
       <c r="I24" s="17" t="n">
         <f aca="false">RANDBETWEEN(-30,90)/1000</f>
-        <v>0.017</v>
+        <v>0.065</v>
       </c>
       <c r="J24" s="17" t="n">
         <f aca="false">+Chạy!K6</f>
@@ -21816,11 +21816,11 @@
       </c>
       <c r="K24" s="17" t="n">
         <f aca="false">J24+L24</f>
-        <v>-0.423</v>
+        <v>-0.397</v>
       </c>
       <c r="L24" s="17" t="n">
         <f aca="false">RANDBETWEEN(-30,90)/1000</f>
-        <v>0.047</v>
+        <v>0.073</v>
       </c>
       <c r="M24" s="17" t="n">
         <f aca="false">+Chạy!N6</f>
@@ -21828,11 +21828,11 @@
       </c>
       <c r="N24" s="17" t="n">
         <f aca="false">+M24+O24</f>
-        <v>8.0435</v>
+        <v>8.0475</v>
       </c>
       <c r="O24" s="17" t="n">
         <f aca="false">RANDBETWEEN(-105,115)/10000</f>
-        <v>-0.0065</v>
+        <v>-0.0025</v>
       </c>
       <c r="P24" s="17" t="n">
         <f aca="false">+Chạy!O6</f>
@@ -21868,11 +21868,11 @@
       </c>
       <c r="E25" s="17" t="n">
         <f aca="false">+D25+F25</f>
-        <v>-8.0476</v>
+        <v>-8.0406</v>
       </c>
       <c r="F25" s="17" t="n">
         <f aca="false">RANDBETWEEN(-105,115)/10000</f>
-        <v>-0.0076</v>
+        <v>-0.0006</v>
       </c>
       <c r="G25" s="17" t="n">
         <f aca="false">+Chạy!G10</f>
@@ -21880,11 +21880,11 @@
       </c>
       <c r="H25" s="17" t="n">
         <f aca="false">G25+I25</f>
-        <v>-0.483</v>
+        <v>-0.503</v>
       </c>
       <c r="I25" s="17" t="n">
         <f aca="false">RANDBETWEEN(-30,90)/1000</f>
-        <v>0.027</v>
+        <v>0.007</v>
       </c>
       <c r="J25" s="17" t="n">
         <f aca="false">+Chạy!K10</f>
@@ -21892,11 +21892,11 @@
       </c>
       <c r="K25" s="17" t="n">
         <f aca="false">J25+L25</f>
-        <v>-0.426</v>
+        <v>-0.454</v>
       </c>
       <c r="L25" s="17" t="n">
         <f aca="false">RANDBETWEEN(-30,90)/1000</f>
-        <v>0.084</v>
+        <v>0.056</v>
       </c>
       <c r="M25" s="17" t="n">
         <f aca="false">+Chạy!N10</f>
@@ -21904,11 +21904,11 @@
       </c>
       <c r="N25" s="17" t="n">
         <f aca="false">+M25+O25</f>
-        <v>8.1006</v>
+        <v>8.0874</v>
       </c>
       <c r="O25" s="17" t="n">
         <f aca="false">RANDBETWEEN(-105,115)/10000</f>
-        <v>0.0106</v>
+        <v>-0.0026</v>
       </c>
       <c r="P25" s="17" t="n">
         <f aca="false">+Chạy!O10</f>
@@ -21916,11 +21916,11 @@
       </c>
       <c r="Q25" s="17" t="n">
         <f aca="false">P25+R25</f>
-        <v>-0.475</v>
+        <v>-0.473</v>
       </c>
       <c r="R25" s="17" t="n">
         <f aca="false">RANDBETWEEN(-30,90)/1000</f>
-        <v>0.035</v>
+        <v>0.037</v>
       </c>
       <c r="S25" s="18"/>
       <c r="T25" s="0" t="n">
@@ -21944,11 +21944,11 @@
       </c>
       <c r="E26" s="17" t="n">
         <f aca="false">+D26+F26</f>
-        <v>-8.2897</v>
+        <v>-8.2722</v>
       </c>
       <c r="F26" s="17" t="n">
         <f aca="false">RANDBETWEEN(-105,115)/10000</f>
-        <v>-0.0097</v>
+        <v>0.0078</v>
       </c>
       <c r="G26" s="17" t="n">
         <f aca="false">+Chạy!G14</f>
@@ -21956,11 +21956,11 @@
       </c>
       <c r="H26" s="17" t="n">
         <f aca="false">G26+I26</f>
-        <v>-0.539</v>
+        <v>-0.522</v>
       </c>
       <c r="I26" s="17" t="n">
         <f aca="false">RANDBETWEEN(-30,90)/1000</f>
-        <v>0.021</v>
+        <v>0.038</v>
       </c>
       <c r="J26" s="17" t="n">
         <f aca="false">+Chạy!K14</f>
@@ -21968,11 +21968,11 @@
       </c>
       <c r="K26" s="17" t="n">
         <f aca="false">J26+L26</f>
-        <v>-0.478</v>
+        <v>-0.587</v>
       </c>
       <c r="L26" s="17" t="n">
         <f aca="false">RANDBETWEEN(-30,90)/1000</f>
-        <v>0.082</v>
+        <v>-0.027</v>
       </c>
       <c r="M26" s="17" t="n">
         <f aca="false">+Chạy!N14</f>
@@ -21980,11 +21980,11 @@
       </c>
       <c r="N26" s="17" t="n">
         <f aca="false">+M26+O26</f>
-        <v>8.259</v>
+        <v>8.251</v>
       </c>
       <c r="O26" s="17" t="n">
         <f aca="false">RANDBETWEEN(-105,115)/10000</f>
-        <v>-0.001</v>
+        <v>-0.009</v>
       </c>
       <c r="P26" s="17" t="n">
         <f aca="false">+Chạy!O14</f>
@@ -21992,11 +21992,11 @@
       </c>
       <c r="Q26" s="17" t="n">
         <f aca="false">P26+R26</f>
-        <v>-0.534</v>
+        <v>-0.564</v>
       </c>
       <c r="R26" s="17" t="n">
         <f aca="false">RANDBETWEEN(-30,90)/1000</f>
-        <v>0.026</v>
+        <v>-0.004</v>
       </c>
       <c r="S26" s="18"/>
       <c r="T26" s="0" t="n">
@@ -22051,11 +22051,11 @@
       </c>
       <c r="E28" s="17" t="n">
         <f aca="false">+D28+F28</f>
-        <v>-5.8244</v>
+        <v>-5.8177</v>
       </c>
       <c r="F28" s="17" t="n">
         <f aca="false">RANDBETWEEN(-105,115)/10000</f>
-        <v>-0.0044</v>
+        <v>0.0023</v>
       </c>
       <c r="G28" s="17" t="n">
         <f aca="false">+Chạy!G22</f>
@@ -22063,11 +22063,11 @@
       </c>
       <c r="H28" s="17" t="n">
         <f aca="false">G28+I28</f>
-        <v>-0.583</v>
+        <v>-0.618</v>
       </c>
       <c r="I28" s="17" t="n">
         <f aca="false">RANDBETWEEN(-30,90)/1000</f>
-        <v>0.047</v>
+        <v>0.012</v>
       </c>
       <c r="J28" s="17" t="n">
         <f aca="false">+Chạy!K22</f>
@@ -22075,11 +22075,11 @@
       </c>
       <c r="K28" s="17" t="n">
         <f aca="false">J28+L28</f>
-        <v>-0.625</v>
+        <v>-0.652</v>
       </c>
       <c r="L28" s="17" t="n">
         <f aca="false">RANDBETWEEN(-30,90)/1000</f>
-        <v>0.005</v>
+        <v>-0.022</v>
       </c>
       <c r="M28" s="17" t="n">
         <f aca="false">+Chạy!N22</f>
@@ -22087,11 +22087,11 @@
       </c>
       <c r="N28" s="17" t="n">
         <f aca="false">+M28+O28</f>
-        <v>8.6769</v>
+        <v>8.6803</v>
       </c>
       <c r="O28" s="17" t="n">
         <f aca="false">RANDBETWEEN(-105,115)/10000</f>
-        <v>-0.0031</v>
+        <v>0.0003</v>
       </c>
       <c r="P28" s="17" t="n">
         <f aca="false">+Chạy!O22</f>
@@ -22099,11 +22099,11 @@
       </c>
       <c r="Q28" s="17" t="n">
         <f aca="false">P28+R28</f>
-        <v>-0.554</v>
+        <v>-0.544</v>
       </c>
       <c r="R28" s="17" t="n">
         <f aca="false">RANDBETWEEN(-30,90)/1000</f>
-        <v>0.076</v>
+        <v>0.086</v>
       </c>
       <c r="S28" s="18"/>
       <c r="T28" s="0" t="n">
@@ -22127,11 +22127,11 @@
       </c>
       <c r="E29" s="17" t="n">
         <f aca="false">+D29+F29</f>
-        <v>-8.6572</v>
+        <v>-8.6598</v>
       </c>
       <c r="F29" s="17" t="n">
         <f aca="false">RANDBETWEEN(-105,115)/10000</f>
-        <v>-0.0072</v>
+        <v>-0.0098</v>
       </c>
       <c r="G29" s="17" t="n">
         <f aca="false">+Chạy!G26</f>
@@ -22139,11 +22139,11 @@
       </c>
       <c r="H29" s="17" t="n">
         <f aca="false">G29+I29</f>
-        <v>-0.596</v>
+        <v>-0.694</v>
       </c>
       <c r="I29" s="17" t="n">
         <f aca="false">RANDBETWEEN(-30,90)/1000</f>
-        <v>0.084</v>
+        <v>-0.014</v>
       </c>
       <c r="J29" s="17" t="n">
         <f aca="false">+Chạy!K26</f>
@@ -22151,11 +22151,11 @@
       </c>
       <c r="K29" s="17" t="n">
         <f aca="false">J29+L29</f>
-        <v>-0.674</v>
+        <v>-0.614</v>
       </c>
       <c r="L29" s="17" t="n">
         <f aca="false">RANDBETWEEN(-30,90)/1000</f>
-        <v>0.006</v>
+        <v>0.066</v>
       </c>
       <c r="M29" s="17" t="n">
         <f aca="false">+Chạy!N26</f>
@@ -22163,11 +22163,11 @@
       </c>
       <c r="N29" s="17" t="n">
         <f aca="false">+M29+O29</f>
-        <v>8.3287</v>
+        <v>8.3196</v>
       </c>
       <c r="O29" s="17" t="n">
         <f aca="false">RANDBETWEEN(-105,115)/10000</f>
-        <v>0.0087</v>
+        <v>-0.0004</v>
       </c>
       <c r="P29" s="17" t="n">
         <f aca="false">+Chạy!O26</f>
@@ -22175,11 +22175,11 @@
       </c>
       <c r="Q29" s="17" t="n">
         <f aca="false">P29+R29</f>
-        <v>-0.617</v>
+        <v>-0.599</v>
       </c>
       <c r="R29" s="17" t="n">
         <f aca="false">RANDBETWEEN(-30,90)/1000</f>
-        <v>0.063</v>
+        <v>0.081</v>
       </c>
       <c r="S29" s="18"/>
       <c r="T29" s="0" t="n">
@@ -22203,11 +22203,11 @@
       </c>
       <c r="E30" s="17" t="n">
         <f aca="false">+D30+F30</f>
-        <v>-8.6239</v>
+        <v>-8.6359</v>
       </c>
       <c r="F30" s="17" t="n">
         <f aca="false">RANDBETWEEN(-105,115)/10000</f>
-        <v>0.0061</v>
+        <v>-0.0059</v>
       </c>
       <c r="G30" s="17" t="n">
         <f aca="false">+Chạy!G30</f>
@@ -22215,11 +22215,11 @@
       </c>
       <c r="H30" s="17" t="n">
         <f aca="false">G30+I30</f>
-        <v>-0.734</v>
+        <v>-0.719</v>
       </c>
       <c r="I30" s="17" t="n">
         <f aca="false">RANDBETWEEN(-30,90)/1000</f>
-        <v>-0.004</v>
+        <v>0.011</v>
       </c>
       <c r="J30" s="17" t="n">
         <f aca="false">+Chạy!K30</f>
@@ -22227,11 +22227,11 @@
       </c>
       <c r="K30" s="17" t="n">
         <f aca="false">J30+L30</f>
-        <v>-0.746</v>
+        <v>-0.644</v>
       </c>
       <c r="L30" s="17" t="n">
         <f aca="false">RANDBETWEEN(-30,90)/1000</f>
-        <v>-0.016</v>
+        <v>0.086</v>
       </c>
       <c r="M30" s="17" t="n">
         <f aca="false">+Chạy!N30</f>
@@ -22239,11 +22239,11 @@
       </c>
       <c r="N30" s="17" t="n">
         <f aca="false">+M30+O30</f>
-        <v>8.143</v>
+        <v>8.1428</v>
       </c>
       <c r="O30" s="17" t="n">
         <f aca="false">RANDBETWEEN(-105,115)/10000</f>
-        <v>-0.007</v>
+        <v>-0.0072</v>
       </c>
       <c r="P30" s="17" t="n">
         <f aca="false">+Chạy!O30</f>
@@ -22251,11 +22251,11 @@
       </c>
       <c r="Q30" s="17" t="n">
         <f aca="false">P30+R30</f>
-        <v>-0.68</v>
+        <v>-0.691</v>
       </c>
       <c r="R30" s="17" t="n">
         <f aca="false">RANDBETWEEN(-30,90)/1000</f>
-        <v>0.05</v>
+        <v>0.039</v>
       </c>
       <c r="S30" s="18"/>
       <c r="T30" s="0" t="n">
@@ -22502,7 +22502,7 @@
     <row r="2" s="26" customFormat="true" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="27" t="str">
         <f>"Kèm theo BBNT số: "&amp;VLOOKUP(AZ2,'[1]Tuyến XB6A'!$A$2:$G$60,7,0)&amp;VLOOKUP(AZ2,'[1]Tuyến XB6A'!$A$2:$G$60,4,0)</f>
-        <v xml:space="preserve">Kèm theo BBNT số: 07.NĐXB6A/CVXD ngày 25 tháng 08 năm 2026</v>
+        <v xml:space="preserve">Kèm theo BBNT số: 07.NĐXB6A/CVXD ngày 28 tháng 08 năm 2026</v>
       </c>
       <c r="B2" s="27"/>
       <c r="C2" s="27"/>
